--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU02/HRM/post DFS_HRM-2031-0452/Panel 02/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU02/HRM/post DFS_HRM-2031-0452/Panel 02/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.15642</v>
+        <v>17.11874</v>
       </c>
       <c r="D2" t="n">
-        <v>16.51504</v>
+        <v>16.58492</v>
       </c>
       <c r="E2" t="n">
-        <v>16.45508</v>
+        <v>16.76606</v>
       </c>
       <c r="F2" t="n">
-        <v>41.88647</v>
+        <v>42.63193</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05012</v>
+        <v>0.05106</v>
       </c>
       <c r="H2" t="n">
-        <v>1.84512</v>
+        <v>1.79415</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.8425</v>
+        <v>16.86373</v>
       </c>
       <c r="D3" t="n">
-        <v>16.42222</v>
+        <v>16.40031</v>
       </c>
       <c r="E3" t="n">
-        <v>16.79585</v>
+        <v>16.67518</v>
       </c>
       <c r="F3" t="n">
-        <v>41.67783</v>
+        <v>42.48304</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0504</v>
+        <v>0.05006</v>
       </c>
       <c r="H3" t="n">
-        <v>1.78483</v>
+        <v>1.82459</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.13583</v>
+        <v>16.91655</v>
       </c>
       <c r="D4" t="n">
-        <v>16.59964</v>
+        <v>16.56029</v>
       </c>
       <c r="E4" t="n">
-        <v>16.90491</v>
+        <v>16.71941</v>
       </c>
       <c r="F4" t="n">
-        <v>42.59778</v>
+        <v>42.29987</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05056</v>
+        <v>0.05024</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82081</v>
+        <v>1.78699</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.60207</v>
+        <v>16.6979</v>
       </c>
       <c r="D6" t="n">
-        <v>16.22331</v>
+        <v>16.055</v>
       </c>
       <c r="E6" t="n">
-        <v>16.24664</v>
+        <v>16.26542</v>
       </c>
       <c r="F6" t="n">
-        <v>21.28713</v>
+        <v>21.38002</v>
       </c>
       <c r="G6" t="n">
-        <v>33.55846</v>
+        <v>34.0565</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.6949</v>
+        <v>16.52991</v>
       </c>
       <c r="D7" t="n">
-        <v>16.22576</v>
+        <v>16.05792</v>
       </c>
       <c r="E7" t="n">
-        <v>16.40466</v>
+        <v>16.45019</v>
       </c>
       <c r="F7" t="n">
-        <v>21.6677</v>
+        <v>21.63564</v>
       </c>
       <c r="G7" t="n">
-        <v>34.61784</v>
+        <v>34.29705</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.70623</v>
+        <v>16.99468</v>
       </c>
       <c r="D8" t="n">
-        <v>16.28172</v>
+        <v>16.09292</v>
       </c>
       <c r="E8" t="n">
-        <v>16.07519</v>
+        <v>16.52217</v>
       </c>
       <c r="F8" t="n">
-        <v>21.10591</v>
+        <v>21.73545</v>
       </c>
       <c r="G8" t="n">
-        <v>34.67392</v>
+        <v>33.32052</v>
       </c>
     </row>
   </sheetData>
